--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-device-request-medicaldevice.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-device-request-medicaldevice.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$96</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2602" uniqueCount="530">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3550" uniqueCount="607">
   <si>
     <t>Property</t>
   </si>
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>DeviceRequest - Medical Device</t>
+    <t>DeviceRequest - Fr git add .Dispositif médical</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-25T15:49:50+00:00</t>
+    <t>2025-09-03T12:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -910,7 +910,7 @@
 PeriodTiming</t>
   </si>
   <si>
-    <t>Date d'utilisation ou de présence chez le patient</t>
+    <t>Desired time or schedule for use</t>
   </si>
   <si>
     <t>The timing schedule for the use of the device. The Schedule data type allows many different expressions, for example. "Every 8 hours"; "Three times a day"; "1/2 an hour before breakfast for 10 days from 23-Dec 2011:"; "15 Oct 2013, 17 Oct 2013 and 1 Nov 2013".</t>
@@ -941,7 +941,7 @@
 </t>
   </si>
   <si>
-    <t>Desired time or schedule for use</t>
+    <t>Date d'utilisation ou de présence chez le patient</t>
   </si>
   <si>
     <t>DeviceRequest.occurrence[x]:occurrenceTiming.id</t>
@@ -1401,7 +1401,7 @@
     <t>DeviceRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitioner-document)
+    <t xml:space="preserve">Reference(Device|Practitioner|PractitionerRole|Organization)
 </t>
   </si>
   <si>
@@ -1421,6 +1421,245 @@
   </si>
   <si>
     <t>FiveWs.author</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur</t>
+  </si>
+  <si>
+    <t>prescripteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Extension - Actor</t>
+  </si>
+  <si>
+    <t>Extension pour représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Type d'acteur (AUT, PRF, PART, INF)</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:type.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.extension.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:type.extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:type.url</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-actor-type</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:reference</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:reference.id</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:reference.extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:reference.url</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.extension:reference.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document)
+</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.url</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension:prescripteur.value[x]</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
+  </si>
+  <si>
+    <t>Reference.reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ref-1
+</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.type</t>
+  </si>
+  <si>
+    <t>Type the reference refers to (e.g. "Patient")</t>
+  </si>
+  <si>
+    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
+The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
+  </si>
+  <si>
+    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+  </si>
+  <si>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.identifier</t>
+  </si>
+  <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
+    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
+  </si>
+  <si>
+    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
+When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
+Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
+Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
+  </si>
+  <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>DeviceRequest.requester.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
+    <t>Reference.display</t>
   </si>
   <si>
     <t>DeviceRequest.performerType</t>
@@ -1457,7 +1696,7 @@
 </t>
   </si>
   <si>
-    <t>Dispensateur</t>
+    <t>Requested Filler</t>
   </si>
   <si>
     <t>The desired performer for doing the diagnostic testing.</t>
@@ -1509,7 +1748,7 @@
     <t>Raisons liées au DM</t>
   </si>
   <si>
-    <t xml:space="preserve">pattern:resolve().code}
+    <t xml:space="preserve">value:resolve().code}
 </t>
   </si>
   <si>
@@ -1977,11 +2216,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO70"/>
+  <dimension ref="A1:AO96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="56.140625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="41.48046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="63.6484375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="45.41796875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="25.1484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1990,7 +2229,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="240.1796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2005,7 +2244,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="108.3203125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="39.265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.4296875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
@@ -5650,7 +5889,7 @@
         <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
@@ -8797,16 +9036,16 @@
         <v>78</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>455</v>
+        <v>241</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>456</v>
+        <v>242</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8833,13 +9072,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>457</v>
+        <v>78</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>458</v>
+        <v>78</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -8857,7 +9096,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>454</v>
+        <v>243</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -8869,19 +9108,19 @@
         <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>459</v>
+        <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>461</v>
+        <v>244</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -8889,41 +9128,43 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>464</v>
+        <v>135</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>465</v>
+        <v>136</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -8960,43 +9201,43 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>463</v>
+        <v>247</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>467</v>
+        <v>78</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>460</v>
+        <v>78</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>468</v>
+        <v>244</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>462</v>
+        <v>78</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9004,12 +9245,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>469</v>
+        <v>456</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C61" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="C61" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="D61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9018,7 +9261,7 @@
         <v>79</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>78</v>
@@ -9027,16 +9270,16 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>254</v>
+        <v>458</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9063,13 +9306,13 @@
         <v>78</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>222</v>
+        <v>78</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>472</v>
+        <v>78</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>473</v>
+        <v>78</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>78</v>
@@ -9087,7 +9330,7 @@
         <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>469</v>
+        <v>247</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>79</v>
@@ -9099,30 +9342,30 @@
         <v>78</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>474</v>
+        <v>78</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>476</v>
+        <v>78</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>478</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>479</v>
+        <v>461</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9133,25 +9376,25 @@
         <v>79</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>480</v>
+        <v>240</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>481</v>
+        <v>241</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>471</v>
+        <v>242</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9190,41 +9433,43 @@
         <v>78</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="AC62" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>226</v>
+        <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>479</v>
+        <v>243</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>484</v>
+        <v>244</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9232,23 +9477,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>485</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C63" t="s" s="2">
-        <v>486</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>79</v>
+        <v>465</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9257,16 +9500,16 @@
         <v>78</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>487</v>
+        <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9305,19 +9548,19 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>479</v>
+        <v>247</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9329,19 +9572,19 @@
         <v>78</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -9349,20 +9592,20 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="D64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>89</v>
@@ -9374,16 +9617,16 @@
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>491</v>
+        <v>135</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9434,7 +9677,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>247</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9446,19 +9689,19 @@
         <v>78</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -9466,14 +9709,12 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>471</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>494</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>78</v>
       </c>
@@ -9491,16 +9732,16 @@
         <v>78</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>495</v>
+        <v>240</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>496</v>
+        <v>241</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>471</v>
+        <v>242</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9551,31 +9792,31 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>479</v>
+        <v>243</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>484</v>
+        <v>244</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -9583,14 +9824,12 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>497</v>
+        <v>473</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>498</v>
-      </c>
+        <v>474</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>78</v>
       </c>
@@ -9599,7 +9838,7 @@
         <v>79</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>78</v>
@@ -9608,16 +9847,16 @@
         <v>78</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>499</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>500</v>
+        <v>466</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9656,19 +9895,19 @@
         <v>78</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>78</v>
+        <v>302</v>
       </c>
       <c r="AC66" t="s" s="2">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="AD66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>78</v>
+        <v>226</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>479</v>
+        <v>247</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>79</v>
@@ -9680,19 +9919,19 @@
         <v>78</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>483</v>
+        <v>78</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>475</v>
+        <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>477</v>
+        <v>78</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -9700,10 +9939,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>501</v>
+        <v>475</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>501</v>
+        <v>476</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9711,10 +9950,10 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>78</v>
@@ -9726,22 +9965,24 @@
         <v>78</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>502</v>
+        <v>103</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>503</v>
+        <v>477</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>478</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>479</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q67" s="2"/>
       <c r="R67" t="s" s="2">
-        <v>78</v>
+        <v>469</v>
       </c>
       <c r="S67" t="s" s="2">
         <v>78</v>
@@ -9783,28 +10024,28 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>501</v>
+        <v>480</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>507</v>
+        <v>132</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>78</v>
@@ -9815,10 +10056,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>481</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>482</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9829,7 +10070,7 @@
         <v>79</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>78</v>
@@ -9841,18 +10082,16 @@
         <v>78</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>509</v>
+        <v>483</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>510</v>
+        <v>484</v>
       </c>
       <c r="N68" s="2"/>
-      <c r="O68" t="s" s="2">
-        <v>511</v>
-      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>78</v>
       </c>
@@ -9876,13 +10115,11 @@
         <v>78</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y68" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="Y68" s="2"/>
       <c r="Z68" t="s" s="2">
-        <v>78</v>
+        <v>485</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>78</v>
@@ -9900,13 +10137,13 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>78</v>
@@ -9915,13 +10152,13 @@
         <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>512</v>
+        <v>78</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>513</v>
+        <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>514</v>
+        <v>132</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>78</v>
@@ -9932,12 +10169,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>515</v>
+        <v>487</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="C69" s="2"/>
+        <v>464</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>488</v>
+      </c>
       <c r="D69" t="s" s="2">
         <v>78</v>
       </c>
@@ -9946,7 +10185,7 @@
         <v>79</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>78</v>
@@ -9958,13 +10197,13 @@
         <v>78</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>516</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>518</v>
+        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10015,7 +10254,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>515</v>
+        <v>247</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10027,30 +10266,30 @@
         <v>78</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>519</v>
+        <v>78</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>520</v>
+        <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>521</v>
+        <v>78</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>522</v>
+        <v>78</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>523</v>
+        <v>490</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>523</v>
+        <v>472</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10061,7 +10300,7 @@
         <v>79</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10073,17 +10312,15 @@
         <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>524</v>
+        <v>240</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>525</v>
+        <v>241</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10132,38 +10369,3054 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="C74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="D74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O77" s="2"/>
+      <c r="P77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="AG70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH70" t="s" s="2">
+      <c r="N83" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G87" t="s" s="2">
         <v>80</v>
       </c>
-      <c r="AI70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ70" t="s" s="2">
+      <c r="H87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
         <v>101</v>
       </c>
-      <c r="AK70" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AK87" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AC88" s="2"/>
+      <c r="AD88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C89" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="D89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="D90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C91" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="D91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="D92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="AM70" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AO70" t="s" s="2">
+      <c r="AM96" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AO96" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO70">
+  <autoFilter ref="A1:AO96">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10173,7 +13426,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI69">
+  <conditionalFormatting sqref="A2:AI95">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-device-request-medicaldevice.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-device-request-medicaldevice.xlsx
@@ -45,7 +45,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>DeviceRequest - Fr git add .Dispositif médical</t>
+    <t>DeviceRequest - Fr Dispositif médical</t>
   </si>
   <si>
     <t>Status</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
